--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574344343</v>
+        <v>46157.93117485436</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93117485436</v>
+        <v>46157.93183363027</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93183363027</v>
+        <v>46157.93405628268</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405628268</v>
+        <v>46157.93723712218</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723712218</v>
+        <v>46158.28221483585</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221483585</v>
+        <v>46158.29701909728</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29701909728</v>
+        <v>46158.29821217608</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821217608</v>
+        <v>46158.33392530428</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392530428</v>
+        <v>46158.36862289755</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862289755</v>
+        <v>46158.37293255596</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
